--- a/www/terminologies/CodeSystem-TRE-R16-LieuFormation.xlsx
+++ b/www/terminologies/CodeSystem-TRE-R16-LieuFormation.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260730120000</t>
+    <t>20260928120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:00:00+01:00</t>
+    <t>2026-09-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -253,7 +253,7 @@
     <t>U34</t>
   </si>
   <si>
-    <t>Université de Montpellier 1 - Nîmes</t>
+    <t>Université de Montpellier - Nîmes</t>
   </si>
   <si>
     <t>U35</t>
@@ -307,7 +307,7 @@
     <t>U59</t>
   </si>
   <si>
-    <t>Lille 2, Université de Droit et Sante</t>
+    <t>Université de Lille</t>
   </si>
   <si>
     <t>U63</t>
